--- a/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 14,72</t>
+          <t>-36,13; 12,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 22,53</t>
+          <t>-24,17; 22,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 23,51</t>
+          <t>-37,3; 22,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 16,21</t>
+          <t>-56,77; 15,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 52,0</t>
+          <t>-63,97; 35,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 91,37</t>
+          <t>-48,31; 87,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,19; 87,8</t>
+          <t>-64,44; 102,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-89,03; 43,0</t>
+          <t>-86,66; 50,17</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 8,99</t>
+          <t>-15,16; 8,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 13,34</t>
+          <t>-8,01; 13,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 14,57</t>
+          <t>-7,38; 14,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 12,41</t>
+          <t>-29,18; 12,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 29,94</t>
+          <t>-36,75; 29,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 37,77</t>
+          <t>-17,76; 35,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 54,09</t>
+          <t>-19,85; 53,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,94; 32,35</t>
+          <t>-58,42; 33,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 3,33</t>
+          <t>-36,23; 5,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 24,72</t>
+          <t>-10,7; 22,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 20,24</t>
+          <t>-18,03; 19,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 16,19</t>
+          <t>-21,18; 15,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 9,59</t>
+          <t>-65,18; 13,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 113,39</t>
+          <t>-27,29; 107,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 63,26</t>
+          <t>-33,74; 59,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 39,85</t>
+          <t>-34,79; 37,17</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 1,27</t>
+          <t>-17,98; 0,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 11,5</t>
+          <t>-5,55; 11,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 11,02</t>
+          <t>-7,22; 11,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 7,81</t>
+          <t>-21,18; 8,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 3,59</t>
+          <t>-39,24; 1,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 33,54</t>
+          <t>-13,26; 32,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 34,85</t>
+          <t>-17,78; 36,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 18,62</t>
+          <t>-44,96; 21,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 12,32</t>
+          <t>-34,79; 12,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 22,0</t>
+          <t>-22,51; 21,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 22,46</t>
+          <t>-36,06; 24,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,77; 15,55</t>
+          <t>-52,89; 12,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,97; 35,7</t>
+          <t>-59,9; 40,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 87,84</t>
+          <t>-46,0; 82,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 102,35</t>
+          <t>-60,32; 98,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-86,66; 50,17</t>
+          <t>-91,22; 30,66</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 8,21</t>
+          <t>-15,6; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 13,13</t>
+          <t>-8,15; 13,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 14,8</t>
+          <t>-7,13; 14,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 12,99</t>
+          <t>-26,85; 12,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 29,35</t>
+          <t>-37,62; 25,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 35,37</t>
+          <t>-17,93; 33,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 53,02</t>
+          <t>-18,53; 50,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 33,38</t>
+          <t>-54,47; 32,84</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 5,45</t>
+          <t>-35,65; 6,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 22,7</t>
+          <t>-11,84; 22,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 19,77</t>
+          <t>-17,59; 20,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 15,31</t>
+          <t>-22,53; 14,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,18; 13,96</t>
+          <t>-63,36; 15,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 107,07</t>
+          <t>-32,44; 101,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 59,99</t>
+          <t>-33,7; 59,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 37,17</t>
+          <t>-36,91; 32,88</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 0,51</t>
+          <t>-17,08; 2,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 11,33</t>
+          <t>-5,23; 12,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 11,68</t>
+          <t>-6,86; 11,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 8,71</t>
+          <t>-23,15; 7,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 1,49</t>
+          <t>-37,89; 6,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 32,22</t>
+          <t>-12,14; 33,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 36,04</t>
+          <t>-16,31; 37,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 21,0</t>
+          <t>-47,8; 18,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-18,96</t>
+          <t>-11,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-42,59%</t>
+          <t>-23,86%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 12,46</t>
+          <t>-33,27; 14,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 21,97</t>
+          <t>-24,1; 22,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 24,48</t>
+          <t>-33,67; 23,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 12,51</t>
+          <t>-44,04; 23,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 40,89</t>
+          <t>-58,75; 52,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 82,75</t>
+          <t>-48,43; 91,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 98,34</t>
+          <t>-60,19; 87,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,22; 30,66</t>
+          <t>-71,71; 74,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>10,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,08%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 8,02</t>
+          <t>-14,09; 8,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 13,0</t>
+          <t>-7,22; 13,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 14,29</t>
+          <t>-6,48; 14,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 12,85</t>
+          <t>-2,69; 21,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 25,06</t>
+          <t>-34,62; 29,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 33,4</t>
+          <t>-16,47; 37,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 50,42</t>
+          <t>-16,73; 54,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,47; 32,84</t>
+          <t>-6,33; 63,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-4,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,74%</t>
+          <t>-7,74%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 6,09</t>
+          <t>-36,18; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 22,29</t>
+          <t>-9,62; 24,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 20,35</t>
+          <t>-15,43; 20,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 14,11</t>
+          <t>-22,19; 15,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,36; 15,56</t>
+          <t>-66,0; 9,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 101,16</t>
+          <t>-26,06; 113,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 59,64</t>
+          <t>-30,94; 63,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 32,88</t>
+          <t>-35,06; 37,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-8,46%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 2,31</t>
+          <t>-18,07; 1,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 12,13</t>
+          <t>-5,29; 11,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 11,7</t>
+          <t>-6,67; 11,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 7,93</t>
+          <t>-4,44; 14,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 6,17</t>
+          <t>-39,06; 3,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 33,94</t>
+          <t>-12,09; 33,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 37,0</t>
+          <t>-16,06; 34,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 18,84</t>
+          <t>-8,95; 37,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-11,43</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-11,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-24,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-18,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-23,86%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.340988579383417</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.452130279559894</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.66328511534558</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.068705813676969</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2177148685083569</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.8639013903038266</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.594272914616817</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3386457557270945</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-33,27; 14,72</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-24,1; 22,53</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-33,67; 23,51</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-44,04; 23,97</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-58,75; 52,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-48,43; 91,37</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-60,19; 87,8</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-71,71; 74,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.625499954721024</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.971938965589696</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.388927104066259</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.12409755723163</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6406753075778872</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4607155937365593</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.8146938308281177</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.639057543126719</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.755512729132219</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.30590426253241</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.440036063950794</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.6703426259751682</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>5.200282460336384</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>0.8303676402069464</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,81</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,85</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-10,45%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-14,09; 8,99</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,22; 13,34</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-6,48; 14,57</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 21,45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-34,62; 29,94</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-16,47; 37,77</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-16,73; 54,09</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-6,33; 63,18</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.3683777987250239</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.547660512104265</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.5396676558244426</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.675564342386204</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.05496621217193137</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.09434170928311322</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1283668939233514</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1858804677640463</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-16,72</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-34,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-7,74%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.255539207121592</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.056657346647836</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.611389901453451</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.154677720579125</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3914007287466131</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4345169538240528</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4756190813057732</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1070485016855854</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-36,18; 3,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,62; 24,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-15,43; 20,24</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-22,19; 15,61</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-66,0; 9,59</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-26,06; 113,39</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-30,94; 63,26</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-35,06; 37,55</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.151083832989541</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.943334410157891</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.532732943003723</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.000649245793737</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3962114270629081</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.447334495478549</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4977511293246809</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.6879365462706994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-7,98</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,73</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-19,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-6.753611122135158</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.2790342152139275</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6789935914736103</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.3562713443634014</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.6169418343341282</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.05717098262754561</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.176543196656988</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.02619867108764262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-18,07; 1,27</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 11,5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,67; 11,02</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 14,82</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-39,06; 3,59</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-12,09; 33,54</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-16,06; 34,85</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-8,95; 37,57</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.04087577744443</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.950500598558741</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.608136962505764</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.606702204533544</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8207924119875024</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6465811606715329</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4933516333158725</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4332516113295202</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-2.486964049895397</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.729064488378273</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.993879583797602</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.91037201059593</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.2549523464500656</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.490121689107347</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.834034145933099</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5942779540942417</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.055195720227228</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.001928660692401829</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1309507165159936</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.7392346167529179</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2531356102487297</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.0003579130238216394</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.03325226120339658</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.07135455125563636</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.119729949635131</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.877423280668372</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.519951932790151</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.129106951242917</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4481493007868522</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2939148581486592</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3174816945821887</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1860052926718669</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.147827142839624</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.217749368096615</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.701109120780015</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.498904727812543</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.02488398754903743</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5009595508740321</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5375322164996861</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3869212450012737</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
